--- a/통합산출물/FILMN9_WBS_v6_Task_Subtask_v2.xlsx
+++ b/통합산출물/FILMN9_WBS_v6_Task_Subtask_v2.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>관리자 페이지 고도화</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>서비스별 테스트 케이스 작성·통합 테스트</t>
+          <t>데이터관리(신선도)·AWS 비용/리소스 모니터링 탭 추가</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>관리자 페이지 고도화</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>비기능 요구사항 검증 (응답속도·보안·면책문구)</t>
+          <t>/admin 접근 토큰 인증 (운영 보안)</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>AWS 클라우드 배포</t>
+          <t>계열회사 시각화 전종목</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>AWS 계정·IAM·VPC·보안그룹 기본 구성</t>
+          <t>사업보고서 RAG → 소유지분도·구조도 SVG 자동 생성 (2,362종)</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>AWS 클라우드 배포</t>
+          <t>계열회사 시각화 전종목</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>RDS PostgreSQL 생성 + 데이터 이전 (16테이블·1,175만행)</t>
+          <t>S3 백업 + EC2 배포 + 종목상세 계열사 토글 연동</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>AWS 클라우드 배포</t>
+          <t>메인페이지 UI 전면 리디자인</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>ChromaDB → EC2(GPU)+EBS 이전 (벡터 ~40GB)</t>
+          <t>통합 스마트검색 (기업+업종 그룹 드롭다운) · 관심종목 즐겨찾기</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>AWS 클라우드 배포</t>
+          <t>메인페이지 UI 전면 리디자인</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>S3 버킷 — Sankey·밸류 JSON·계열사 이미지 서빙</t>
+          <t>추천종목 캐러셀(밸류·DCF 충실)·업종 둘러보기·중앙 정렬·하위화면 브레드크럼</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>AWS 클라우드 배포</t>
+          <t>글로벌 마켓 시그널 확장</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>EC2 — FastAPI 백엔드 / 프론트 배포 (uvicorn·nginx)</t>
+          <t>미국 3대 지수(다우·나스닥·S&amp;P)·상해종합·공포탐욕 추가 / 카테고리 접기·펴기</t>
         </is>
       </c>
     </row>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>AWS 클라우드 배포</t>
+          <t>MCP 서버</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>MongoDB Atlas 화이트리스트 / Secrets Manager / 도메인·SSL</t>
+          <t>FINSIGHT MCP 설계 + 동작 서버(4개 도구) 구현 (발표 어필)</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>3차 배포·산출물 패키징</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>최종 서비스 안정화 / README·깃허브 코드 정리</t>
+          <t>서비스별 테스트 케이스 작성·통합 테스트</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>3차 배포·산출물 패키징</t>
+          <t>QA</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>전체 산출물 패키징 (기획서·WBS·요구사항·아키텍처·코드·배포URL)</t>
+          <t>비기능 요구사항 검증 (응답속도·보안·면책문구)</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>발표 준비</t>
+          <t>AWS 클라우드 배포</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>최종 발표 PPT 제작 (데모·히스토리 브리핑·Valuation·차별점)</t>
+          <t>AWS 계정·IAM·VPC·보안그룹 기본 구성</t>
         </is>
       </c>
     </row>
@@ -1737,27 +1737,163 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>발표 준비</t>
+          <t>AWS 클라우드 배포</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>발표 리허설·레슨런 / 4차 멘토링 (6/13)</t>
+          <t>RDS PostgreSQL 생성 + 데이터 이전 (16테이블·1,175만행)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>스프린트 5 (06/08~06/19)</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>AWS 클라우드 배포</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>ChromaDB → EC2(GPU)+EBS 이전 (벡터 ~40GB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>스프린트 5 (06/08~06/19)</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>AWS 클라우드 배포</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>S3 버킷 — Sankey·밸류 JSON·계열사 이미지 서빙</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>스프린트 5 (06/08~06/19)</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>AWS 클라우드 배포</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>EC2 — FastAPI 백엔드 / 프론트 배포 (uvicorn·nginx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>스프린트 5 (06/08~06/19)</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>AWS 클라우드 배포</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>MongoDB Atlas 화이트리스트 / Secrets Manager / 도메인·SSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>스프린트 5 (06/08~06/19)</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>3차 배포·산출물 패키징</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>최종 서비스 안정화 / README·깃허브 코드 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>스프린트 5 (06/08~06/19)</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>3차 배포·산출물 패키징</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>전체 산출물 패키징 (기획서·WBS·요구사항·아키텍처·코드·배포URL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>스프린트 5 (06/08~06/19)</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>발표 준비</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>최종 발표 PPT 제작 (데모·히스토리 브리핑·Valuation·차별점)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>스프린트 5 (06/08~06/19)</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>발표 준비</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>발표 리허설·레슨런 / 4차 멘토링 (6/13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
           <t>최종 발표 (06/20)</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>최종 발표</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>최종 발표 및 수료</t>
         </is>
